--- a/Employee_Reports_wi52/Sameera Lakmal Rupasinghe Arachchige Q0577.xlsx
+++ b/Employee_Reports_wi52/Sameera Lakmal Rupasinghe Arachchige Q0577.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-98</v>
+        <v>-106</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-97</v>
+        <v>-105</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-93</v>
+        <v>-101</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-84</v>
+        <v>-92</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-86</v>
+        <v>-94</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-90</v>
+        <v>-98</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-71</v>
+        <v>-79</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-92</v>
+        <v>-100</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-114</v>
+        <v>-122</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-440</v>
+        <v>-448</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-463</v>
+        <v>-471</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-378</v>
+        <v>-386</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-163</v>
+        <v>-171</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-160</v>
+        <v>-168</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-148</v>
+        <v>-156</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
